--- a/data_lake/datos_diarios_preliminares/dt=2026-09-04/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-09-04/temperaturamed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436E655F-8A70-460B-95F4-3C4095741299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D94C88-2901-465E-B877-ADED8D0DACA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$A$4:$AS$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6354,8 +6353,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="152" width="32.42578125" style="50" customWidth="1"/>
-    <col min="153" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="153" width="32.42578125" style="50" customWidth="1"/>
+    <col min="154" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6644,7 +6643,9 @@
       <c r="L5" s="56">
         <v>30.1</v>
       </c>
-      <c r="M5" s="56"/>
+      <c r="M5" s="56">
+        <v>30</v>
+      </c>
       <c r="N5" s="56"/>
       <c r="O5" s="56"/>
       <c r="P5" s="56"/>
@@ -6675,7 +6676,7 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ5" s="71" t="str">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
@@ -6727,7 +6728,9 @@
       <c r="L6" s="56">
         <v>29.7</v>
       </c>
-      <c r="M6" s="56"/>
+      <c r="M6" s="56">
+        <v>29.8</v>
+      </c>
       <c r="N6" s="56"/>
       <c r="O6" s="56"/>
       <c r="P6" s="56"/>
@@ -6758,7 +6761,7 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ6" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6810,7 +6813,9 @@
       <c r="L7" s="56">
         <v>31</v>
       </c>
-      <c r="M7" s="56"/>
+      <c r="M7" s="56">
+        <v>31.5</v>
+      </c>
       <c r="N7" s="56"/>
       <c r="O7" s="56"/>
       <c r="P7" s="56"/>
@@ -6841,7 +6846,7 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ7" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6893,7 +6898,9 @@
       <c r="L8" s="56">
         <v>30.5</v>
       </c>
-      <c r="M8" s="56"/>
+      <c r="M8" s="56">
+        <v>30.5</v>
+      </c>
       <c r="N8" s="56"/>
       <c r="O8" s="56"/>
       <c r="P8" s="56"/>
@@ -6924,7 +6931,7 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ8" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6976,7 +6983,9 @@
       <c r="L9" s="56">
         <v>30.4</v>
       </c>
-      <c r="M9" s="56"/>
+      <c r="M9" s="56">
+        <v>30.4</v>
+      </c>
       <c r="N9" s="56"/>
       <c r="O9" s="56"/>
       <c r="P9" s="56"/>
@@ -7007,7 +7016,7 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ9" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7059,7 +7068,9 @@
       <c r="L10" s="56">
         <v>30.5</v>
       </c>
-      <c r="M10" s="56"/>
+      <c r="M10" s="56">
+        <v>33.299999999999997</v>
+      </c>
       <c r="N10" s="56"/>
       <c r="O10" s="56"/>
       <c r="P10" s="56"/>
@@ -7090,7 +7101,7 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ10" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7142,7 +7153,9 @@
       <c r="L11" s="56">
         <v>31.6</v>
       </c>
-      <c r="M11" s="56"/>
+      <c r="M11" s="56">
+        <v>32.799999999999997</v>
+      </c>
       <c r="N11" s="56"/>
       <c r="O11" s="56"/>
       <c r="P11" s="56"/>
@@ -7173,7 +7186,7 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ11" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7225,7 +7238,9 @@
       <c r="L12" s="56">
         <v>29.9</v>
       </c>
-      <c r="M12" s="56"/>
+      <c r="M12" s="56">
+        <v>30.5</v>
+      </c>
       <c r="N12" s="56"/>
       <c r="O12" s="56"/>
       <c r="P12" s="56"/>
@@ -7256,7 +7271,7 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ12" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7308,7 +7323,9 @@
       <c r="L13" s="56">
         <v>29.9</v>
       </c>
-      <c r="M13" s="56"/>
+      <c r="M13" s="56">
+        <v>29.8</v>
+      </c>
       <c r="N13" s="56"/>
       <c r="O13" s="56"/>
       <c r="P13" s="56"/>
@@ -7339,7 +7356,7 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ13" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7391,7 +7408,9 @@
       <c r="L14" s="56">
         <v>23</v>
       </c>
-      <c r="M14" s="56"/>
+      <c r="M14" s="56">
+        <v>23.4</v>
+      </c>
       <c r="N14" s="56"/>
       <c r="O14" s="56"/>
       <c r="P14" s="56"/>
@@ -7422,7 +7441,7 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ14" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7474,7 +7493,9 @@
       <c r="L15" s="56">
         <v>29.6</v>
       </c>
-      <c r="M15" s="56"/>
+      <c r="M15" s="56">
+        <v>31.1</v>
+      </c>
       <c r="N15" s="56"/>
       <c r="O15" s="56"/>
       <c r="P15" s="56"/>
@@ -7505,7 +7526,7 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ15" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7557,7 +7578,9 @@
       <c r="L16" s="56">
         <v>28.7</v>
       </c>
-      <c r="M16" s="56"/>
+      <c r="M16" s="56">
+        <v>29.1</v>
+      </c>
       <c r="N16" s="56"/>
       <c r="O16" s="56"/>
       <c r="P16" s="56"/>
@@ -7588,7 +7611,7 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ16" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7640,7 +7663,9 @@
       <c r="L17" s="56">
         <v>24.8</v>
       </c>
-      <c r="M17" s="56"/>
+      <c r="M17" s="56">
+        <v>26.5</v>
+      </c>
       <c r="N17" s="56"/>
       <c r="O17" s="56"/>
       <c r="P17" s="56"/>
@@ -7671,7 +7696,7 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ17" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7723,7 +7748,9 @@
       <c r="L18" s="56">
         <v>18.5</v>
       </c>
-      <c r="M18" s="56"/>
+      <c r="M18" s="56">
+        <v>19.2</v>
+      </c>
       <c r="N18" s="56"/>
       <c r="O18" s="56"/>
       <c r="P18" s="56"/>
@@ -7754,7 +7781,7 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ18" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7806,7 +7833,9 @@
       <c r="L19" s="56">
         <v>24</v>
       </c>
-      <c r="M19" s="56"/>
+      <c r="M19" s="56">
+        <v>25.1</v>
+      </c>
       <c r="N19" s="56"/>
       <c r="O19" s="56"/>
       <c r="P19" s="56"/>
@@ -7837,7 +7866,7 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7889,7 +7918,9 @@
       <c r="L20" s="56">
         <v>25.1</v>
       </c>
-      <c r="M20" s="56"/>
+      <c r="M20" s="56">
+        <v>25.9</v>
+      </c>
       <c r="N20" s="56"/>
       <c r="O20" s="56"/>
       <c r="P20" s="56"/>
@@ -7920,7 +7951,7 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ20" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7972,7 +8003,9 @@
       <c r="L21" s="56">
         <v>26.8</v>
       </c>
-      <c r="M21" s="56"/>
+      <c r="M21" s="56">
+        <v>28.3</v>
+      </c>
       <c r="N21" s="56"/>
       <c r="O21" s="56"/>
       <c r="P21" s="56"/>
@@ -8003,7 +8036,7 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ21" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8055,7 +8088,9 @@
       <c r="L22" s="56">
         <v>15.6</v>
       </c>
-      <c r="M22" s="56"/>
+      <c r="M22" s="56">
+        <v>16</v>
+      </c>
       <c r="N22" s="56"/>
       <c r="O22" s="56"/>
       <c r="P22" s="56"/>
@@ -8086,7 +8121,7 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8138,7 +8173,9 @@
       <c r="L23" s="56">
         <v>27.1</v>
       </c>
-      <c r="M23" s="56"/>
+      <c r="M23" s="56">
+        <v>27.5</v>
+      </c>
       <c r="N23" s="56"/>
       <c r="O23" s="56"/>
       <c r="P23" s="56"/>
@@ -8169,7 +8206,7 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ23" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8221,7 +8258,9 @@
       <c r="L24" s="56">
         <v>30</v>
       </c>
-      <c r="M24" s="56"/>
+      <c r="M24" s="56">
+        <v>29.7</v>
+      </c>
       <c r="N24" s="56"/>
       <c r="O24" s="56"/>
       <c r="P24" s="56"/>
@@ -8252,7 +8291,7 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ24" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8304,7 +8343,9 @@
       <c r="L25" s="56">
         <v>22.2</v>
       </c>
-      <c r="M25" s="56"/>
+      <c r="M25" s="56">
+        <v>23.6</v>
+      </c>
       <c r="N25" s="56"/>
       <c r="O25" s="56"/>
       <c r="P25" s="56"/>
@@ -8335,7 +8376,7 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ25" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8387,7 +8428,9 @@
       <c r="L26" s="56">
         <v>10.7</v>
       </c>
-      <c r="M26" s="56"/>
+      <c r="M26" s="56">
+        <v>10.8</v>
+      </c>
       <c r="N26" s="56"/>
       <c r="O26" s="56"/>
       <c r="P26" s="56"/>
@@ -8418,7 +8461,7 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ26" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8470,7 +8513,9 @@
       <c r="L27" s="56">
         <v>26.7</v>
       </c>
-      <c r="M27" s="56"/>
+      <c r="M27" s="56">
+        <v>28.3</v>
+      </c>
       <c r="N27" s="56"/>
       <c r="O27" s="56"/>
       <c r="P27" s="56"/>
@@ -8501,7 +8546,7 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ27" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8553,7 +8598,9 @@
       <c r="L28" s="56">
         <v>24.2</v>
       </c>
-      <c r="M28" s="56"/>
+      <c r="M28" s="56">
+        <v>29.2</v>
+      </c>
       <c r="N28" s="56"/>
       <c r="O28" s="56"/>
       <c r="P28" s="56"/>
@@ -8584,7 +8631,7 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ28" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8636,7 +8683,9 @@
       <c r="L29" s="56">
         <v>27.3</v>
       </c>
-      <c r="M29" s="56"/>
+      <c r="M29" s="56">
+        <v>28.4</v>
+      </c>
       <c r="N29" s="56"/>
       <c r="O29" s="56"/>
       <c r="P29" s="56"/>
@@ -8667,7 +8716,7 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ29" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8719,7 +8768,9 @@
       <c r="L30" s="56">
         <v>25.8</v>
       </c>
-      <c r="M30" s="56"/>
+      <c r="M30" s="56">
+        <v>27.8</v>
+      </c>
       <c r="N30" s="56"/>
       <c r="O30" s="56"/>
       <c r="P30" s="56"/>
@@ -8750,7 +8801,7 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ30" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8802,7 +8853,9 @@
       <c r="L31" s="98">
         <v>28.5</v>
       </c>
-      <c r="M31" s="98"/>
+      <c r="M31" s="98">
+        <v>28.4</v>
+      </c>
       <c r="N31" s="98"/>
       <c r="O31" s="98"/>
       <c r="P31" s="98"/>
@@ -8833,7 +8886,7 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ31" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8885,7 +8938,9 @@
       <c r="L32" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="M32" s="56"/>
+      <c r="M32" s="56">
+        <v>20.100000000000001</v>
+      </c>
       <c r="N32" s="56"/>
       <c r="O32" s="56"/>
       <c r="P32" s="56"/>
@@ -8916,7 +8971,7 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ32" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8968,7 +9023,9 @@
       <c r="L33" s="56">
         <v>28.65</v>
       </c>
-      <c r="M33" s="56"/>
+      <c r="M33" s="56">
+        <v>27.3</v>
+      </c>
       <c r="N33" s="56"/>
       <c r="O33" s="56"/>
       <c r="P33" s="56"/>
@@ -8999,7 +9056,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9051,7 +9108,9 @@
       <c r="L34" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="M34" s="56"/>
+      <c r="M34" s="56">
+        <v>21.733333333333331</v>
+      </c>
       <c r="N34" s="56"/>
       <c r="O34" s="56"/>
       <c r="P34" s="56"/>
@@ -9082,7 +9141,7 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ34" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9134,7 +9193,9 @@
       <c r="L35" s="56">
         <v>24.2</v>
       </c>
-      <c r="M35" s="56"/>
+      <c r="M35" s="56">
+        <v>24.8</v>
+      </c>
       <c r="N35" s="56"/>
       <c r="O35" s="56"/>
       <c r="P35" s="56"/>
@@ -9165,7 +9226,7 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ35" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9217,7 +9278,9 @@
       <c r="L36" s="56">
         <v>19.649999999999999</v>
       </c>
-      <c r="M36" s="56"/>
+      <c r="M36" s="56">
+        <v>20.3</v>
+      </c>
       <c r="N36" s="56"/>
       <c r="O36" s="56"/>
       <c r="P36" s="56"/>
@@ -9248,7 +9311,7 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ36" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9300,7 +9363,9 @@
       <c r="L37" s="56">
         <v>27.8</v>
       </c>
-      <c r="M37" s="56"/>
+      <c r="M37" s="56">
+        <v>28.5</v>
+      </c>
       <c r="N37" s="56"/>
       <c r="O37" s="56"/>
       <c r="P37" s="56"/>
@@ -9331,7 +9396,7 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ37" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9383,7 +9448,9 @@
       <c r="L38" s="56">
         <v>16.05</v>
       </c>
-      <c r="M38" s="56"/>
+      <c r="M38" s="56">
+        <v>16.5</v>
+      </c>
       <c r="N38" s="56"/>
       <c r="O38" s="56"/>
       <c r="P38" s="56"/>
@@ -9414,7 +9481,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9466,7 +9533,9 @@
       <c r="L39" s="56">
         <v>22.13333333333334</v>
       </c>
-      <c r="M39" s="56"/>
+      <c r="M39" s="56">
+        <v>23.13333333333334</v>
+      </c>
       <c r="N39" s="56"/>
       <c r="O39" s="56"/>
       <c r="P39" s="56"/>
@@ -9497,7 +9566,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9549,7 +9618,9 @@
       <c r="L40" s="56">
         <v>24.266666666666669</v>
       </c>
-      <c r="M40" s="56"/>
+      <c r="M40" s="56">
+        <v>26.13333333333334</v>
+      </c>
       <c r="N40" s="56"/>
       <c r="O40" s="56"/>
       <c r="P40" s="56"/>
@@ -9580,7 +9651,7 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ40" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9632,7 +9703,9 @@
       <c r="L41" s="56">
         <v>18.666666666666671</v>
       </c>
-      <c r="M41" s="56"/>
+      <c r="M41" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="N41" s="56"/>
       <c r="O41" s="56"/>
       <c r="P41" s="56"/>
@@ -9663,7 +9736,7 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ41" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9715,7 +9788,9 @@
       <c r="L42" s="56">
         <v>28.1</v>
       </c>
-      <c r="M42" s="56"/>
+      <c r="M42" s="56">
+        <v>29.05</v>
+      </c>
       <c r="N42" s="56"/>
       <c r="O42" s="56"/>
       <c r="P42" s="56"/>
@@ -9746,7 +9821,7 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ42" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9798,7 +9873,9 @@
       <c r="L43" s="56">
         <v>30</v>
       </c>
-      <c r="M43" s="56"/>
+      <c r="M43" s="56">
+        <v>29</v>
+      </c>
       <c r="N43" s="56"/>
       <c r="O43" s="56"/>
       <c r="P43" s="56"/>
@@ -9829,7 +9906,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9881,7 +9958,9 @@
       <c r="L44" s="56">
         <v>28.35</v>
       </c>
-      <c r="M44" s="56"/>
+      <c r="M44" s="56">
+        <v>29.25</v>
+      </c>
       <c r="N44" s="56"/>
       <c r="O44" s="56"/>
       <c r="P44" s="56"/>
@@ -9912,7 +9991,7 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ44" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9964,7 +10043,9 @@
       <c r="L45" s="56">
         <v>29</v>
       </c>
-      <c r="M45" s="56"/>
+      <c r="M45" s="56">
+        <v>28.95</v>
+      </c>
       <c r="N45" s="56"/>
       <c r="O45" s="56"/>
       <c r="P45" s="56"/>
@@ -9995,7 +10076,7 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ45" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10047,7 +10128,9 @@
       <c r="L46" s="56">
         <v>28.4</v>
       </c>
-      <c r="M46" s="56"/>
+      <c r="M46" s="56">
+        <v>28.9</v>
+      </c>
       <c r="N46" s="56"/>
       <c r="O46" s="56"/>
       <c r="P46" s="56"/>
@@ -10078,7 +10161,7 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ46" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10130,7 +10213,9 @@
       <c r="L47" s="56">
         <v>30.266666666666669</v>
       </c>
-      <c r="M47" s="56"/>
+      <c r="M47" s="56">
+        <v>30.266666666666669</v>
+      </c>
       <c r="N47" s="56"/>
       <c r="O47" s="56"/>
       <c r="P47" s="56"/>
@@ -10161,7 +10246,7 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ47" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10371,7 +10456,9 @@
       <c r="L50" s="56">
         <v>27.5</v>
       </c>
-      <c r="M50" s="56"/>
+      <c r="M50" s="56">
+        <v>29.45</v>
+      </c>
       <c r="N50" s="56"/>
       <c r="O50" s="56"/>
       <c r="P50" s="56"/>
@@ -10402,7 +10489,7 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ50" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10612,7 +10699,9 @@
       <c r="L53" s="56">
         <v>28.35</v>
       </c>
-      <c r="M53" s="56"/>
+      <c r="M53" s="56">
+        <v>28.7</v>
+      </c>
       <c r="N53" s="56"/>
       <c r="O53" s="56"/>
       <c r="P53" s="56"/>
@@ -10643,7 +10732,7 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10695,7 +10784,9 @@
       <c r="L54" s="56">
         <v>29.9</v>
       </c>
-      <c r="M54" s="56"/>
+      <c r="M54" s="56">
+        <v>30.7</v>
+      </c>
       <c r="N54" s="56"/>
       <c r="O54" s="56"/>
       <c r="P54" s="56"/>
@@ -10726,7 +10817,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10776,7 +10867,9 @@
       <c r="L55" s="56">
         <v>30.6</v>
       </c>
-      <c r="M55" s="56"/>
+      <c r="M55" s="56">
+        <v>30.6</v>
+      </c>
       <c r="N55" s="56"/>
       <c r="O55" s="56"/>
       <c r="P55" s="56"/>
@@ -10807,7 +10900,7 @@
       <c r="AO55" s="56"/>
       <c r="AP55" s="58">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ55" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11096,7 +11189,9 @@
       <c r="L59" s="56">
         <v>30.2</v>
       </c>
-      <c r="M59" s="56"/>
+      <c r="M59" s="56">
+        <v>28.1</v>
+      </c>
       <c r="N59" s="56"/>
       <c r="O59" s="56"/>
       <c r="P59" s="56"/>
@@ -11127,7 +11222,7 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ59" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11260,7 +11355,9 @@
       <c r="L61" s="56">
         <v>28.35</v>
       </c>
-      <c r="M61" s="56"/>
+      <c r="M61" s="56">
+        <v>28.25</v>
+      </c>
       <c r="N61" s="56"/>
       <c r="O61" s="56"/>
       <c r="P61" s="56"/>
@@ -11291,7 +11388,7 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ61" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11339,7 +11436,9 @@
       </c>
       <c r="K62" s="56"/>
       <c r="L62" s="56"/>
-      <c r="M62" s="56"/>
+      <c r="M62" s="56">
+        <v>29</v>
+      </c>
       <c r="N62" s="56"/>
       <c r="O62" s="56"/>
       <c r="P62" s="56"/>
@@ -11370,7 +11469,7 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ62" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11661,7 +11760,9 @@
       <c r="L66" s="56">
         <v>27.9</v>
       </c>
-      <c r="M66" s="56"/>
+      <c r="M66" s="56">
+        <v>26.6</v>
+      </c>
       <c r="N66" s="56"/>
       <c r="O66" s="56"/>
       <c r="P66" s="56"/>
@@ -11692,7 +11793,7 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ66" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11744,7 +11845,9 @@
       <c r="L67" s="56">
         <v>26.9</v>
       </c>
-      <c r="M67" s="56"/>
+      <c r="M67" s="56">
+        <v>26.75</v>
+      </c>
       <c r="N67" s="56"/>
       <c r="O67" s="56"/>
       <c r="P67" s="56"/>
@@ -11775,7 +11878,7 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ67" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11827,7 +11930,9 @@
       <c r="L68" s="56">
         <v>24.75</v>
       </c>
-      <c r="M68" s="56"/>
+      <c r="M68" s="56">
+        <v>26.15</v>
+      </c>
       <c r="N68" s="56"/>
       <c r="O68" s="56"/>
       <c r="P68" s="56"/>
@@ -11858,7 +11963,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11910,7 +12015,9 @@
       <c r="L69" s="56">
         <v>27.35</v>
       </c>
-      <c r="M69" s="56"/>
+      <c r="M69" s="56">
+        <v>26.65</v>
+      </c>
       <c r="N69" s="56"/>
       <c r="O69" s="56"/>
       <c r="P69" s="56"/>
@@ -11941,7 +12048,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -11993,7 +12100,9 @@
       <c r="L70" s="56">
         <v>28.13333333333334</v>
       </c>
-      <c r="M70" s="56"/>
+      <c r="M70" s="56">
+        <v>28.2</v>
+      </c>
       <c r="N70" s="56"/>
       <c r="O70" s="56"/>
       <c r="P70" s="56"/>
@@ -12024,7 +12133,7 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ70" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12076,7 +12185,9 @@
       <c r="L71" s="56">
         <v>27.233333333333331</v>
       </c>
-      <c r="M71" s="56"/>
+      <c r="M71" s="56">
+        <v>27.766666666666669</v>
+      </c>
       <c r="N71" s="56"/>
       <c r="O71" s="56"/>
       <c r="P71" s="56"/>
@@ -12107,7 +12218,7 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ71" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12159,7 +12270,9 @@
       <c r="L72" s="56">
         <v>26.166666666666671</v>
       </c>
-      <c r="M72" s="56"/>
+      <c r="M72" s="56">
+        <v>26.966666666666669</v>
+      </c>
       <c r="N72" s="56"/>
       <c r="O72" s="56"/>
       <c r="P72" s="56"/>
@@ -12190,7 +12303,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12242,7 +12355,9 @@
       <c r="L73" s="56">
         <v>26.9</v>
       </c>
-      <c r="M73" s="56"/>
+      <c r="M73" s="56">
+        <v>25.55</v>
+      </c>
       <c r="N73" s="56"/>
       <c r="O73" s="56"/>
       <c r="P73" s="56"/>
@@ -12273,7 +12388,7 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ73" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12325,7 +12440,9 @@
       <c r="L74" s="56">
         <v>20.6</v>
       </c>
-      <c r="M74" s="56"/>
+      <c r="M74" s="56">
+        <v>21.95</v>
+      </c>
       <c r="N74" s="56"/>
       <c r="O74" s="56"/>
       <c r="P74" s="56"/>
@@ -12356,7 +12473,7 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ74" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12408,7 +12525,9 @@
       <c r="L75" s="56">
         <v>16.466666666666669</v>
       </c>
-      <c r="M75" s="56"/>
+      <c r="M75" s="56">
+        <v>15.6</v>
+      </c>
       <c r="N75" s="56"/>
       <c r="O75" s="56"/>
       <c r="P75" s="56"/>
@@ -12439,7 +12558,7 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ75" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12491,7 +12610,9 @@
       <c r="L76" s="56">
         <v>20.95</v>
       </c>
-      <c r="M76" s="56"/>
+      <c r="M76" s="56">
+        <v>21.55</v>
+      </c>
       <c r="N76" s="56"/>
       <c r="O76" s="56"/>
       <c r="P76" s="56"/>
@@ -12522,7 +12643,7 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ76" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12574,7 +12695,9 @@
       <c r="L77" s="56">
         <v>24.06666666666667</v>
       </c>
-      <c r="M77" s="56"/>
+      <c r="M77" s="56">
+        <v>24.6</v>
+      </c>
       <c r="N77" s="56"/>
       <c r="O77" s="56"/>
       <c r="P77" s="56"/>
@@ -12605,7 +12728,7 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ77" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12657,7 +12780,9 @@
       <c r="L78" s="56">
         <v>31.9</v>
       </c>
-      <c r="M78" s="56"/>
+      <c r="M78" s="56">
+        <v>31.3</v>
+      </c>
       <c r="N78" s="56"/>
       <c r="O78" s="56"/>
       <c r="P78" s="56"/>
@@ -12688,7 +12813,7 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ78" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12740,7 +12865,9 @@
       <c r="L79" s="56">
         <v>32.133333333333333</v>
       </c>
-      <c r="M79" s="56"/>
+      <c r="M79" s="56">
+        <v>31.466666666666669</v>
+      </c>
       <c r="N79" s="56"/>
       <c r="O79" s="56"/>
       <c r="P79" s="56"/>
@@ -12771,7 +12898,7 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ79" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12904,7 +13031,9 @@
       <c r="L81" s="56">
         <v>25.5</v>
       </c>
-      <c r="M81" s="56"/>
+      <c r="M81" s="56">
+        <v>26.3</v>
+      </c>
       <c r="N81" s="56"/>
       <c r="O81" s="56"/>
       <c r="P81" s="56"/>
@@ -12935,7 +13064,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -12987,7 +13116,9 @@
       <c r="L82" s="56">
         <v>27.13333333333334</v>
       </c>
-      <c r="M82" s="56"/>
+      <c r="M82" s="56">
+        <v>27.933333333333341</v>
+      </c>
       <c r="N82" s="56"/>
       <c r="O82" s="56"/>
       <c r="P82" s="56"/>
@@ -13018,7 +13149,7 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ82" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13228,7 +13359,9 @@
       <c r="L85" s="56">
         <v>29.85</v>
       </c>
-      <c r="M85" s="56"/>
+      <c r="M85" s="56">
+        <v>32.5</v>
+      </c>
       <c r="N85" s="56"/>
       <c r="O85" s="56"/>
       <c r="P85" s="56"/>
@@ -13259,7 +13392,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13311,7 +13444,9 @@
       <c r="L86" s="56">
         <v>29.75</v>
       </c>
-      <c r="M86" s="56"/>
+      <c r="M86" s="56">
+        <v>30</v>
+      </c>
       <c r="N86" s="56"/>
       <c r="O86" s="56"/>
       <c r="P86" s="56"/>
@@ -13342,7 +13477,7 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ86" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13394,7 +13529,9 @@
       <c r="L87" s="56">
         <v>30.7</v>
       </c>
-      <c r="M87" s="56"/>
+      <c r="M87" s="56">
+        <v>31.2</v>
+      </c>
       <c r="N87" s="56"/>
       <c r="O87" s="56"/>
       <c r="P87" s="56"/>
@@ -13425,7 +13562,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13477,7 +13614,9 @@
       <c r="L88" s="56">
         <v>29.65</v>
       </c>
-      <c r="M88" s="56"/>
+      <c r="M88" s="56">
+        <v>29.65</v>
+      </c>
       <c r="N88" s="56"/>
       <c r="O88" s="56"/>
       <c r="P88" s="56"/>
@@ -13508,7 +13647,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13558,7 +13697,9 @@
         <v>26.8</v>
       </c>
       <c r="L89" s="56"/>
-      <c r="M89" s="56"/>
+      <c r="M89" s="56">
+        <v>31.05</v>
+      </c>
       <c r="N89" s="56"/>
       <c r="O89" s="56"/>
       <c r="P89" s="56"/>
@@ -13589,7 +13730,7 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ89" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13641,7 +13782,9 @@
       <c r="L90" s="56">
         <v>30.05</v>
       </c>
-      <c r="M90" s="56"/>
+      <c r="M90" s="56">
+        <v>30.8</v>
+      </c>
       <c r="N90" s="56"/>
       <c r="O90" s="56"/>
       <c r="P90" s="56"/>
@@ -13672,7 +13815,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13720,7 +13863,9 @@
       </c>
       <c r="K91" s="56"/>
       <c r="L91" s="56"/>
-      <c r="M91" s="56"/>
+      <c r="M91" s="56">
+        <v>30.25</v>
+      </c>
       <c r="N91" s="56"/>
       <c r="O91" s="56"/>
       <c r="P91" s="56"/>
@@ -13751,7 +13896,7 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ91" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13803,7 +13948,9 @@
       <c r="L92" s="56">
         <v>17.95</v>
       </c>
-      <c r="M92" s="56"/>
+      <c r="M92" s="56">
+        <v>18.55</v>
+      </c>
       <c r="N92" s="56"/>
       <c r="O92" s="56"/>
       <c r="P92" s="56"/>
@@ -13834,7 +13981,7 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ92" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13886,7 +14033,9 @@
       <c r="L93" s="56">
         <v>24.8</v>
       </c>
-      <c r="M93" s="56"/>
+      <c r="M93" s="56">
+        <v>25.4</v>
+      </c>
       <c r="N93" s="56"/>
       <c r="O93" s="56"/>
       <c r="P93" s="56"/>
@@ -13917,7 +14066,7 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ93" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13969,7 +14118,9 @@
       <c r="L94" s="56">
         <v>17.45</v>
       </c>
-      <c r="M94" s="56"/>
+      <c r="M94" s="56">
+        <v>18</v>
+      </c>
       <c r="N94" s="56"/>
       <c r="O94" s="56"/>
       <c r="P94" s="56"/>
@@ -14000,7 +14151,7 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ94" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14052,7 +14203,9 @@
       <c r="L95" s="56">
         <v>14.6</v>
       </c>
-      <c r="M95" s="56"/>
+      <c r="M95" s="56">
+        <v>13.35</v>
+      </c>
       <c r="N95" s="56"/>
       <c r="O95" s="56"/>
       <c r="P95" s="56"/>
@@ -14083,7 +14236,7 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ95" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14214,7 +14367,9 @@
       <c r="L97" s="56">
         <v>17.333333333333329</v>
       </c>
-      <c r="M97" s="56"/>
+      <c r="M97" s="56">
+        <v>18</v>
+      </c>
       <c r="N97" s="56"/>
       <c r="O97" s="56"/>
       <c r="P97" s="56"/>
@@ -14245,7 +14400,7 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ97" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14297,7 +14452,9 @@
       <c r="L98" s="56">
         <v>13.15</v>
       </c>
-      <c r="M98" s="56"/>
+      <c r="M98" s="56">
+        <v>12.95</v>
+      </c>
       <c r="N98" s="56"/>
       <c r="O98" s="56"/>
       <c r="P98" s="56"/>
@@ -14328,7 +14485,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14380,7 +14537,9 @@
       <c r="L99" s="56">
         <v>14.93333333333333</v>
       </c>
-      <c r="M99" s="56"/>
+      <c r="M99" s="56">
+        <v>15.5</v>
+      </c>
       <c r="N99" s="56"/>
       <c r="O99" s="56"/>
       <c r="P99" s="56"/>
@@ -14411,7 +14570,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14463,7 +14622,9 @@
       <c r="L100" s="56">
         <v>16.333333333333329</v>
       </c>
-      <c r="M100" s="56"/>
+      <c r="M100" s="56">
+        <v>15.733333333333331</v>
+      </c>
       <c r="N100" s="56"/>
       <c r="O100" s="56"/>
       <c r="P100" s="56"/>
@@ -14494,7 +14655,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14546,7 +14707,9 @@
       <c r="L101" s="56">
         <v>13</v>
       </c>
-      <c r="M101" s="56"/>
+      <c r="M101" s="56">
+        <v>13.3</v>
+      </c>
       <c r="N101" s="56"/>
       <c r="O101" s="56"/>
       <c r="P101" s="56"/>
@@ -14577,7 +14740,7 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ101" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14625,7 +14788,9 @@
       </c>
       <c r="K102" s="56"/>
       <c r="L102" s="56"/>
-      <c r="M102" s="56"/>
+      <c r="M102" s="56">
+        <v>14</v>
+      </c>
       <c r="N102" s="56"/>
       <c r="O102" s="56"/>
       <c r="P102" s="56"/>
@@ -14656,7 +14821,7 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ102" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14866,7 +15031,9 @@
       <c r="L105" s="56">
         <v>20.2</v>
       </c>
-      <c r="M105" s="56"/>
+      <c r="M105" s="56">
+        <v>20.733333333333331</v>
+      </c>
       <c r="N105" s="56"/>
       <c r="O105" s="56"/>
       <c r="P105" s="56"/>
@@ -14897,7 +15064,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15109,7 +15276,9 @@
       <c r="L108" s="56">
         <v>13.45</v>
       </c>
-      <c r="M108" s="56"/>
+      <c r="M108" s="56">
+        <v>13.05</v>
+      </c>
       <c r="N108" s="56"/>
       <c r="O108" s="56"/>
       <c r="P108" s="56"/>
@@ -15140,7 +15309,7 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ108" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15192,7 +15361,9 @@
       <c r="L109" s="56">
         <v>14.65</v>
       </c>
-      <c r="M109" s="56"/>
+      <c r="M109" s="56">
+        <v>14.35</v>
+      </c>
       <c r="N109" s="56"/>
       <c r="O109" s="56"/>
       <c r="P109" s="56"/>
@@ -15223,7 +15394,7 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ109" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15273,7 +15444,9 @@
       <c r="L110" s="56">
         <v>18.13333333333334</v>
       </c>
-      <c r="M110" s="56"/>
+      <c r="M110" s="56">
+        <v>17</v>
+      </c>
       <c r="N110" s="56"/>
       <c r="O110" s="56"/>
       <c r="P110" s="56"/>
@@ -15304,7 +15477,7 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ110" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15356,7 +15529,9 @@
       <c r="L111" s="56">
         <v>16</v>
       </c>
-      <c r="M111" s="56"/>
+      <c r="M111" s="56">
+        <v>15.266666666666669</v>
+      </c>
       <c r="N111" s="56"/>
       <c r="O111" s="56"/>
       <c r="P111" s="56"/>
@@ -15387,7 +15562,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15439,7 +15614,9 @@
       <c r="L112" s="56">
         <v>18.866666666666671</v>
       </c>
-      <c r="M112" s="56"/>
+      <c r="M112" s="56">
+        <v>18.2</v>
+      </c>
       <c r="N112" s="56"/>
       <c r="O112" s="56"/>
       <c r="P112" s="56"/>
@@ -15470,7 +15647,7 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ112" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15603,7 +15780,9 @@
       <c r="L114" s="56">
         <v>22.333333333333329</v>
       </c>
-      <c r="M114" s="56"/>
+      <c r="M114" s="56">
+        <v>22.2</v>
+      </c>
       <c r="N114" s="56"/>
       <c r="O114" s="56"/>
       <c r="P114" s="56"/>
@@ -15634,7 +15813,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15686,7 +15865,9 @@
       <c r="L115" s="56">
         <v>27.55</v>
       </c>
-      <c r="M115" s="56"/>
+      <c r="M115" s="56">
+        <v>28.35</v>
+      </c>
       <c r="N115" s="56"/>
       <c r="O115" s="56"/>
       <c r="P115" s="56"/>
@@ -15717,7 +15898,7 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ115" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15769,7 +15950,9 @@
       <c r="L116" s="56">
         <v>19.266666666666669</v>
       </c>
-      <c r="M116" s="56"/>
+      <c r="M116" s="56">
+        <v>20</v>
+      </c>
       <c r="N116" s="56"/>
       <c r="O116" s="56"/>
       <c r="P116" s="56"/>
@@ -15800,7 +15983,7 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ116" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15852,7 +16035,9 @@
       <c r="L117" s="56">
         <v>26.933333333333341</v>
       </c>
-      <c r="M117" s="56"/>
+      <c r="M117" s="56">
+        <v>27.93333333333333</v>
+      </c>
       <c r="N117" s="56"/>
       <c r="O117" s="56"/>
       <c r="P117" s="56"/>
@@ -15883,7 +16068,7 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ117" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16014,7 +16199,9 @@
       <c r="L119" s="56">
         <v>23.93333333333333</v>
       </c>
-      <c r="M119" s="56"/>
+      <c r="M119" s="56">
+        <v>25</v>
+      </c>
       <c r="N119" s="56"/>
       <c r="O119" s="56"/>
       <c r="P119" s="56"/>
@@ -16045,7 +16232,7 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ119" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16255,7 +16442,9 @@
       <c r="L122" s="56">
         <v>13</v>
       </c>
-      <c r="M122" s="56"/>
+      <c r="M122" s="56">
+        <v>11.866666666666671</v>
+      </c>
       <c r="N122" s="56"/>
       <c r="O122" s="56"/>
       <c r="P122" s="56"/>
@@ -16286,7 +16475,7 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ122" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16417,7 +16606,9 @@
       <c r="L124" s="56">
         <v>15.6</v>
       </c>
-      <c r="M124" s="56"/>
+      <c r="M124" s="56">
+        <v>16.13333333333334</v>
+      </c>
       <c r="N124" s="56"/>
       <c r="O124" s="56"/>
       <c r="P124" s="56"/>
@@ -16448,7 +16639,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16899,7 +17090,9 @@
       <c r="L130" s="56">
         <v>15.6</v>
       </c>
-      <c r="M130" s="56"/>
+      <c r="M130" s="56">
+        <v>15.7</v>
+      </c>
       <c r="N130" s="56"/>
       <c r="O130" s="56"/>
       <c r="P130" s="56"/>
@@ -16930,7 +17123,7 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ130" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16982,7 +17175,9 @@
       <c r="L131" s="56">
         <v>19.350000000000001</v>
       </c>
-      <c r="M131" s="56"/>
+      <c r="M131" s="56">
+        <v>18.05</v>
+      </c>
       <c r="N131" s="56"/>
       <c r="O131" s="56"/>
       <c r="P131" s="56"/>
@@ -17013,7 +17208,7 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ131" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17144,7 +17339,9 @@
       <c r="L133" s="56">
         <v>14.366666666666671</v>
       </c>
-      <c r="M133" s="56"/>
+      <c r="M133" s="56">
+        <v>13.733333333333331</v>
+      </c>
       <c r="N133" s="56"/>
       <c r="O133" s="56"/>
       <c r="P133" s="56"/>
@@ -17175,7 +17372,7 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ133" s="71" t="str">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
@@ -17227,7 +17424,9 @@
       <c r="L134" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="M134" s="56"/>
+      <c r="M134" s="56">
+        <v>17.2</v>
+      </c>
       <c r="N134" s="56"/>
       <c r="O134" s="56"/>
       <c r="P134" s="56"/>
@@ -17258,7 +17457,7 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ134" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17310,7 +17509,9 @@
       <c r="L135" s="56">
         <v>19.899999999999999</v>
       </c>
-      <c r="M135" s="56"/>
+      <c r="M135" s="56">
+        <v>22.65</v>
+      </c>
       <c r="N135" s="56"/>
       <c r="O135" s="56"/>
       <c r="P135" s="56"/>
@@ -17341,7 +17542,7 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ135" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17553,7 +17754,9 @@
       <c r="L138" s="56">
         <v>21.733333333333331</v>
       </c>
-      <c r="M138" s="56"/>
+      <c r="M138" s="56">
+        <v>22.6</v>
+      </c>
       <c r="N138" s="56"/>
       <c r="O138" s="56"/>
       <c r="P138" s="56"/>
@@ -17584,7 +17787,7 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ138" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17636,7 +17839,9 @@
       <c r="L139" s="56">
         <v>14.75</v>
       </c>
-      <c r="M139" s="56"/>
+      <c r="M139" s="56">
+        <v>13.275</v>
+      </c>
       <c r="N139" s="56"/>
       <c r="O139" s="56"/>
       <c r="P139" s="56"/>
@@ -17667,7 +17872,7 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ139" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17719,7 +17924,9 @@
       <c r="L140" s="56">
         <v>16</v>
       </c>
-      <c r="M140" s="56"/>
+      <c r="M140" s="56">
+        <v>15.4</v>
+      </c>
       <c r="N140" s="56"/>
       <c r="O140" s="56"/>
       <c r="P140" s="56"/>
@@ -17750,7 +17957,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17802,7 +18009,9 @@
       <c r="L141" s="56">
         <v>13.66666666666667</v>
       </c>
-      <c r="M141" s="56"/>
+      <c r="M141" s="56">
+        <v>13.133333333333329</v>
+      </c>
       <c r="N141" s="56"/>
       <c r="O141" s="56"/>
       <c r="P141" s="56"/>
@@ -17833,7 +18042,7 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ141" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17885,7 +18094,9 @@
       <c r="L142" s="56">
         <v>12.2</v>
       </c>
-      <c r="M142" s="56"/>
+      <c r="M142" s="56">
+        <v>11.475</v>
+      </c>
       <c r="N142" s="56"/>
       <c r="O142" s="56"/>
       <c r="P142" s="56"/>
@@ -17916,7 +18127,7 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ142" s="71" t="str">
         <f t="shared" si="7"/>
@@ -17968,7 +18179,9 @@
       <c r="L143" s="56">
         <v>28.533333333333331</v>
       </c>
-      <c r="M143" s="56"/>
+      <c r="M143" s="56">
+        <v>28.066666666666659</v>
+      </c>
       <c r="N143" s="56"/>
       <c r="O143" s="56"/>
       <c r="P143" s="56"/>
@@ -17999,7 +18212,7 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ143" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18051,7 +18264,9 @@
       <c r="L144" s="56">
         <v>16.2</v>
       </c>
-      <c r="M144" s="56"/>
+      <c r="M144" s="56">
+        <v>16.2</v>
+      </c>
       <c r="N144" s="56"/>
       <c r="O144" s="56"/>
       <c r="P144" s="56"/>
@@ -18082,7 +18297,7 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ144" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18134,7 +18349,9 @@
       <c r="L145" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="M145" s="56"/>
+      <c r="M145" s="56">
+        <v>21.466666666666669</v>
+      </c>
       <c r="N145" s="56"/>
       <c r="O145" s="56"/>
       <c r="P145" s="56"/>
@@ -18165,7 +18382,7 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ145" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18214,8 +18431,12 @@
       <c r="K146" s="56">
         <v>30.533333333333331</v>
       </c>
-      <c r="L146" s="56"/>
-      <c r="M146" s="56"/>
+      <c r="L146" s="56">
+        <v>30.466666666666669</v>
+      </c>
+      <c r="M146" s="56">
+        <v>31.06666666666667</v>
+      </c>
       <c r="N146" s="56"/>
       <c r="O146" s="56"/>
       <c r="P146" s="56"/>
@@ -18246,7 +18467,7 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ146" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18298,7 +18519,9 @@
       <c r="L147" s="56">
         <v>26</v>
       </c>
-      <c r="M147" s="56"/>
+      <c r="M147" s="56">
+        <v>26.93333333333333</v>
+      </c>
       <c r="N147" s="56"/>
       <c r="O147" s="56"/>
       <c r="P147" s="56"/>
@@ -18329,7 +18552,7 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ147" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18381,7 +18604,9 @@
       <c r="L148" s="56">
         <v>30.666666666666671</v>
       </c>
-      <c r="M148" s="56"/>
+      <c r="M148" s="56">
+        <v>29.4</v>
+      </c>
       <c r="N148" s="56"/>
       <c r="O148" s="56"/>
       <c r="P148" s="56"/>
@@ -18412,7 +18637,7 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ148" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18461,8 +18686,12 @@
       <c r="K149" s="56">
         <v>22.8</v>
       </c>
-      <c r="L149" s="56"/>
-      <c r="M149" s="56"/>
+      <c r="L149" s="56">
+        <v>21.733333333333331</v>
+      </c>
+      <c r="M149" s="56">
+        <v>23.4</v>
+      </c>
       <c r="N149" s="56"/>
       <c r="O149" s="56"/>
       <c r="P149" s="56"/>
@@ -18493,7 +18722,7 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ149" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18865,7 +19094,9 @@
       <c r="L154" s="56">
         <v>19.75</v>
       </c>
-      <c r="M154" s="56"/>
+      <c r="M154" s="56">
+        <v>21.55</v>
+      </c>
       <c r="N154" s="56"/>
       <c r="O154" s="56"/>
       <c r="P154" s="56"/>
@@ -18896,7 +19127,7 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ154" s="71" t="str">
         <f t="shared" si="7"/>
@@ -18948,7 +19179,9 @@
       <c r="L155" s="56">
         <v>28.733333333333331</v>
       </c>
-      <c r="M155" s="56"/>
+      <c r="M155" s="56">
+        <v>29.466666666666669</v>
+      </c>
       <c r="N155" s="56"/>
       <c r="O155" s="56"/>
       <c r="P155" s="56"/>
@@ -18979,7 +19212,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19193,7 +19426,9 @@
       <c r="L158" s="56">
         <v>30.86666666666666</v>
       </c>
-      <c r="M158" s="56"/>
+      <c r="M158" s="56">
+        <v>30</v>
+      </c>
       <c r="N158" s="56"/>
       <c r="O158" s="56"/>
       <c r="P158" s="56"/>
@@ -19224,7 +19459,7 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ158" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19276,7 +19511,9 @@
       <c r="L159" s="56">
         <v>20.133333333333329</v>
       </c>
-      <c r="M159" s="56"/>
+      <c r="M159" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="N159" s="56"/>
       <c r="O159" s="56"/>
       <c r="P159" s="56"/>
@@ -19307,7 +19544,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19359,7 +19596,9 @@
       <c r="L160" s="56">
         <v>27.266666666666669</v>
       </c>
-      <c r="M160" s="56"/>
+      <c r="M160" s="56">
+        <v>26.86666666666666</v>
+      </c>
       <c r="N160" s="56"/>
       <c r="O160" s="56"/>
       <c r="P160" s="56"/>
@@ -19390,7 +19629,7 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ160" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19521,7 +19760,9 @@
       <c r="L162" s="56">
         <v>28.533333333333331</v>
       </c>
-      <c r="M162" s="56"/>
+      <c r="M162" s="56">
+        <v>29.266666666666669</v>
+      </c>
       <c r="N162" s="56"/>
       <c r="O162" s="56"/>
       <c r="P162" s="56"/>
@@ -19552,7 +19793,7 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ162" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19604,7 +19845,9 @@
       <c r="L163" s="56">
         <v>21.466666666666669</v>
       </c>
-      <c r="M163" s="56"/>
+      <c r="M163" s="56">
+        <v>22.13333333333334</v>
+      </c>
       <c r="N163" s="56"/>
       <c r="O163" s="56"/>
       <c r="P163" s="56"/>
@@ -19635,7 +19878,7 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ163" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19687,7 +19930,9 @@
       <c r="L164" s="56">
         <v>25.9</v>
       </c>
-      <c r="M164" s="56"/>
+      <c r="M164" s="56">
+        <v>25.3</v>
+      </c>
       <c r="N164" s="56"/>
       <c r="O164" s="56"/>
       <c r="P164" s="56"/>
@@ -19718,7 +19963,7 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ164" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19846,8 +20091,12 @@
       <c r="K166" s="56">
         <v>14.93333333333333</v>
       </c>
-      <c r="L166" s="56"/>
-      <c r="M166" s="56"/>
+      <c r="L166" s="56">
+        <v>14.6</v>
+      </c>
+      <c r="M166" s="56">
+        <v>14.7</v>
+      </c>
       <c r="N166" s="56"/>
       <c r="O166" s="56"/>
       <c r="P166" s="56"/>
@@ -19878,7 +20127,7 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ166" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19930,7 +20179,9 @@
       <c r="L167" s="56">
         <v>20.733333333333331</v>
       </c>
-      <c r="M167" s="56"/>
+      <c r="M167" s="56">
+        <v>20.399999999999999</v>
+      </c>
       <c r="N167" s="56"/>
       <c r="O167" s="56"/>
       <c r="P167" s="56"/>
@@ -19961,7 +20212,7 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ167" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20013,7 +20264,9 @@
       <c r="L168" s="56">
         <v>28.3</v>
       </c>
-      <c r="M168" s="56"/>
+      <c r="M168" s="56">
+        <v>28.35</v>
+      </c>
       <c r="N168" s="56"/>
       <c r="O168" s="56"/>
       <c r="P168" s="56"/>
@@ -20044,7 +20297,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20096,7 +20349,9 @@
       <c r="L169" s="56">
         <v>10</v>
       </c>
-      <c r="M169" s="56"/>
+      <c r="M169" s="56">
+        <v>9.7000000000000011</v>
+      </c>
       <c r="N169" s="56"/>
       <c r="O169" s="56"/>
       <c r="P169" s="56"/>
@@ -20127,7 +20382,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20179,7 +20434,9 @@
       <c r="L170" s="56">
         <v>23.86666666666666</v>
       </c>
-      <c r="M170" s="56"/>
+      <c r="M170" s="56">
+        <v>26.6</v>
+      </c>
       <c r="N170" s="56"/>
       <c r="O170" s="56"/>
       <c r="P170" s="56"/>
@@ -20210,7 +20467,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20262,7 +20519,9 @@
       <c r="L171" s="56">
         <v>22.13333333333334</v>
       </c>
-      <c r="M171" s="56"/>
+      <c r="M171" s="56">
+        <v>20.86666666666666</v>
+      </c>
       <c r="N171" s="56"/>
       <c r="O171" s="56"/>
       <c r="P171" s="56"/>
@@ -20293,7 +20552,7 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ171" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20345,7 +20604,9 @@
       <c r="L172" s="56">
         <v>26.45</v>
       </c>
-      <c r="M172" s="56"/>
+      <c r="M172" s="56">
+        <v>26.75</v>
+      </c>
       <c r="N172" s="56"/>
       <c r="O172" s="56"/>
       <c r="P172" s="56"/>
@@ -20376,7 +20637,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20428,7 +20689,9 @@
       <c r="L173" s="56">
         <v>26.1</v>
       </c>
-      <c r="M173" s="56"/>
+      <c r="M173" s="56">
+        <v>25.95</v>
+      </c>
       <c r="N173" s="56"/>
       <c r="O173" s="56"/>
       <c r="P173" s="56"/>
@@ -20459,7 +20722,7 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ173" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20511,7 +20774,9 @@
       <c r="L174" s="56">
         <v>12.266666666666669</v>
       </c>
-      <c r="M174" s="56"/>
+      <c r="M174" s="56">
+        <v>12.266666666666669</v>
+      </c>
       <c r="N174" s="56"/>
       <c r="O174" s="56"/>
       <c r="P174" s="56"/>
@@ -20542,7 +20807,7 @@
       <c r="AO174" s="56"/>
       <c r="AP174" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ174" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20828,8 +21093,12 @@
       <c r="K178" s="56">
         <v>24.466666666666669</v>
       </c>
-      <c r="L178" s="56"/>
-      <c r="M178" s="56"/>
+      <c r="L178" s="56">
+        <v>25.4</v>
+      </c>
+      <c r="M178" s="56">
+        <v>25.4</v>
+      </c>
       <c r="N178" s="56"/>
       <c r="O178" s="56"/>
       <c r="P178" s="56"/>
@@ -20860,7 +21129,7 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ178" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20912,7 +21181,9 @@
       <c r="L179" s="56">
         <v>18.8</v>
       </c>
-      <c r="M179" s="56"/>
+      <c r="M179" s="56">
+        <v>18.649999999999999</v>
+      </c>
       <c r="N179" s="56"/>
       <c r="O179" s="56"/>
       <c r="P179" s="56"/>
@@ -20943,7 +21214,7 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ179" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21074,7 +21345,9 @@
       <c r="L181" s="56">
         <v>32.4</v>
       </c>
-      <c r="M181" s="56"/>
+      <c r="M181" s="56">
+        <v>30.93333333333333</v>
+      </c>
       <c r="N181" s="56"/>
       <c r="O181" s="56"/>
       <c r="P181" s="56"/>
@@ -21105,7 +21378,7 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ181" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21315,7 +21588,9 @@
       <c r="L184" s="56">
         <v>27.666666666666671</v>
       </c>
-      <c r="M184" s="56"/>
+      <c r="M184" s="56">
+        <v>27.6</v>
+      </c>
       <c r="N184" s="56"/>
       <c r="O184" s="56"/>
       <c r="P184" s="56"/>
@@ -21346,7 +21621,7 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ184" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21398,7 +21673,9 @@
       <c r="L185" s="56">
         <v>30.8</v>
       </c>
-      <c r="M185" s="56"/>
+      <c r="M185" s="56">
+        <v>30.2</v>
+      </c>
       <c r="N185" s="56"/>
       <c r="O185" s="56"/>
       <c r="P185" s="56"/>
@@ -21429,7 +21706,7 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ185" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21639,7 +21916,9 @@
       <c r="L188" s="56">
         <v>17.06666666666667</v>
       </c>
-      <c r="M188" s="56"/>
+      <c r="M188" s="56">
+        <v>17.466666666666669</v>
+      </c>
       <c r="N188" s="56"/>
       <c r="O188" s="56"/>
       <c r="P188" s="56"/>
@@ -21670,7 +21949,7 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ188" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21805,7 +22084,9 @@
       <c r="L190" s="56">
         <v>29.6</v>
       </c>
-      <c r="M190" s="56"/>
+      <c r="M190" s="56">
+        <v>31.2</v>
+      </c>
       <c r="N190" s="56"/>
       <c r="O190" s="56"/>
       <c r="P190" s="56"/>
@@ -21836,7 +22117,7 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ190" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21888,7 +22169,9 @@
       <c r="L191" s="56">
         <v>18.95</v>
       </c>
-      <c r="M191" s="56"/>
+      <c r="M191" s="56">
+        <v>18.899999999999999</v>
+      </c>
       <c r="N191" s="56"/>
       <c r="O191" s="56"/>
       <c r="P191" s="56"/>
@@ -21919,7 +22202,7 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ191" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21971,7 +22254,9 @@
       <c r="L192" s="56">
         <v>25.86666666666666</v>
       </c>
-      <c r="M192" s="56"/>
+      <c r="M192" s="56">
+        <v>25.4</v>
+      </c>
       <c r="N192" s="56"/>
       <c r="O192" s="56"/>
       <c r="P192" s="56"/>
@@ -22002,7 +22287,7 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ192" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22054,7 +22339,9 @@
       <c r="L193" s="56">
         <v>30.3</v>
       </c>
-      <c r="M193" s="56"/>
+      <c r="M193" s="56">
+        <v>30.4</v>
+      </c>
       <c r="N193" s="56"/>
       <c r="O193" s="56"/>
       <c r="P193" s="56"/>
@@ -22085,7 +22372,7 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ193" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22137,7 +22424,9 @@
       <c r="L194" s="56">
         <v>22.2</v>
       </c>
-      <c r="M194" s="56"/>
+      <c r="M194" s="56">
+        <v>21.8</v>
+      </c>
       <c r="N194" s="56"/>
       <c r="O194" s="56"/>
       <c r="P194" s="56"/>
@@ -22168,7 +22457,7 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ194" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22220,7 +22509,9 @@
       <c r="L195" s="56">
         <v>27</v>
       </c>
-      <c r="M195" s="56"/>
+      <c r="M195" s="56">
+        <v>27.733333333333331</v>
+      </c>
       <c r="N195" s="56"/>
       <c r="O195" s="56"/>
       <c r="P195" s="56"/>
@@ -22251,7 +22542,7 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ195" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22303,7 +22594,9 @@
       <c r="L196" s="56">
         <v>20.866666666666671</v>
       </c>
-      <c r="M196" s="56"/>
+      <c r="M196" s="56">
+        <v>23.066666666666659</v>
+      </c>
       <c r="N196" s="56"/>
       <c r="O196" s="56"/>
       <c r="P196" s="56"/>
@@ -22334,7 +22627,7 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ196" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22386,7 +22679,9 @@
       <c r="L197" s="56">
         <v>26.733333333333331</v>
       </c>
-      <c r="M197" s="56"/>
+      <c r="M197" s="56">
+        <v>26.533333333333331</v>
+      </c>
       <c r="N197" s="56"/>
       <c r="O197" s="56"/>
       <c r="P197" s="56"/>
@@ -22417,7 +22712,7 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ197" s="71" t="str">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
@@ -22469,7 +22764,9 @@
       <c r="L198" s="56">
         <v>22.05</v>
       </c>
-      <c r="M198" s="56"/>
+      <c r="M198" s="56">
+        <v>21.9</v>
+      </c>
       <c r="N198" s="56"/>
       <c r="O198" s="56"/>
       <c r="P198" s="56"/>
@@ -22500,7 +22797,7 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ198" s="71" t="str">
         <f t="shared" si="10"/>
@@ -22552,7 +22849,9 @@
       <c r="L199" s="56">
         <v>16.333333333333329</v>
       </c>
-      <c r="M199" s="56"/>
+      <c r="M199" s="56">
+        <v>16.733333333333331</v>
+      </c>
       <c r="N199" s="56"/>
       <c r="O199" s="56"/>
       <c r="P199" s="56"/>
@@ -22583,7 +22882,7 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ199" s="71" t="str">
         <f t="shared" si="10"/>
@@ -22635,7 +22934,9 @@
       <c r="L200" s="56">
         <v>14.5</v>
       </c>
-      <c r="M200" s="56"/>
+      <c r="M200" s="56">
+        <v>14.3</v>
+      </c>
       <c r="N200" s="56"/>
       <c r="O200" s="56"/>
       <c r="P200" s="56"/>
@@ -22666,7 +22967,7 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ200" s="71" t="str">
         <f t="shared" si="10"/>
@@ -22718,7 +23019,9 @@
       <c r="L201" s="56">
         <v>27.95</v>
       </c>
-      <c r="M201" s="56"/>
+      <c r="M201" s="56">
+        <v>28.25</v>
+      </c>
       <c r="N201" s="56"/>
       <c r="O201" s="56"/>
       <c r="P201" s="56"/>
@@ -22749,7 +23052,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -22884,7 +23187,9 @@
       <c r="L203" s="56">
         <v>14</v>
       </c>
-      <c r="M203" s="56"/>
+      <c r="M203" s="56">
+        <v>14.2</v>
+      </c>
       <c r="N203" s="56"/>
       <c r="O203" s="56"/>
       <c r="P203" s="56"/>
@@ -22915,7 +23220,7 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ203" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23046,7 +23351,9 @@
       <c r="L205" s="56">
         <v>14.6</v>
       </c>
-      <c r="M205" s="56"/>
+      <c r="M205" s="56">
+        <v>15.5</v>
+      </c>
       <c r="N205" s="56"/>
       <c r="O205" s="56"/>
       <c r="P205" s="56"/>
@@ -23077,7 +23384,7 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ205" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23129,7 +23436,9 @@
       <c r="L206" s="56">
         <v>14.35</v>
       </c>
-      <c r="M206" s="56"/>
+      <c r="M206" s="56">
+        <v>13.5</v>
+      </c>
       <c r="N206" s="56"/>
       <c r="O206" s="56"/>
       <c r="P206" s="56"/>
@@ -23160,7 +23469,7 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ206" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23212,7 +23521,9 @@
       <c r="L207" s="56">
         <v>13.866666666666671</v>
       </c>
-      <c r="M207" s="56"/>
+      <c r="M207" s="56">
+        <v>13.8</v>
+      </c>
       <c r="N207" s="56"/>
       <c r="O207" s="56"/>
       <c r="P207" s="56"/>
@@ -23243,7 +23554,7 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ207" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23295,7 +23606,9 @@
       <c r="L208" s="56">
         <v>14.25</v>
       </c>
-      <c r="M208" s="56"/>
+      <c r="M208" s="56">
+        <v>13.45</v>
+      </c>
       <c r="N208" s="56"/>
       <c r="O208" s="56"/>
       <c r="P208" s="56"/>
@@ -23326,7 +23639,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23378,7 +23691,9 @@
       <c r="L209" s="56">
         <v>11.25</v>
       </c>
-      <c r="M209" s="56"/>
+      <c r="M209" s="56">
+        <v>11.05</v>
+      </c>
       <c r="N209" s="56"/>
       <c r="O209" s="56"/>
       <c r="P209" s="56"/>
@@ -23409,7 +23724,7 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ209" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23461,7 +23776,9 @@
       <c r="L210" s="56">
         <v>15.35</v>
       </c>
-      <c r="M210" s="56"/>
+      <c r="M210" s="56">
+        <v>15.35</v>
+      </c>
       <c r="N210" s="56"/>
       <c r="O210" s="56"/>
       <c r="P210" s="56"/>
@@ -23492,7 +23809,7 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ210" s="71" t="str">
         <f t="shared" si="10"/>
@@ -23627,7 +23944,9 @@
       <c r="L212" s="56">
         <v>28.7</v>
       </c>
-      <c r="M212" s="56"/>
+      <c r="M212" s="56">
+        <v>28.75</v>
+      </c>
       <c r="N212" s="56"/>
       <c r="O212" s="56"/>
       <c r="P212" s="56"/>
@@ -23658,7 +23977,7 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ212" s="71" t="str">
         <f t="shared" si="10"/>
